--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L349"/>
+  <dimension ref="A1:L490"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18573,6 +18573,7338 @@
       <c r="L349" t="inlineStr">
         <is>
           <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Inca Aruba vs Alianza</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Inca Aruba</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F350" t="n">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I350" t="n">
+        <v>0</v>
+      </c>
+      <c r="J350" t="n">
+        <v>0</v>
+      </c>
+      <c r="K350" t="n">
+        <v>0</v>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Minnesota United FC vs Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Minnesota United FC</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F351" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I351" t="n">
+        <v>0</v>
+      </c>
+      <c r="J351" t="n">
+        <v>0</v>
+      </c>
+      <c r="K351" t="n">
+        <v>0</v>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Lanus vs San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F352" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I352" t="n">
+        <v>0</v>
+      </c>
+      <c r="J352" t="n">
+        <v>0</v>
+      </c>
+      <c r="K352" t="n">
+        <v>0</v>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>FC Tulsa vs Lexington</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>FC Tulsa</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F353" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I353" t="n">
+        <v>0</v>
+      </c>
+      <c r="J353" t="n">
+        <v>0</v>
+      </c>
+      <c r="K353" t="n">
+        <v>0</v>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Cashmere Technical vs Miramar</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Cashmere Technical</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F354" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="n">
+        <v>0</v>
+      </c>
+      <c r="K354" t="n">
+        <v>0</v>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Malacateco vs Cobán Imperial</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Malacateco</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F355" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" t="n">
+        <v>0</v>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Monarcas vs CA La Paz</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>CA La Paz</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F356" t="n">
+        <v>84.7</v>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I356" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" t="n">
+        <v>0</v>
+      </c>
+      <c r="K356" t="n">
+        <v>0</v>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>CDS Tampico Madero vs Piratas</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>CDS Tampico Madero</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F357" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I357" t="n">
+        <v>0</v>
+      </c>
+      <c r="J357" t="n">
+        <v>0</v>
+      </c>
+      <c r="K357" t="n">
+        <v>0</v>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Nelson Suburbs vs Auckland United</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Auckland United</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F358" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I358" t="n">
+        <v>0</v>
+      </c>
+      <c r="J358" t="n">
+        <v>0</v>
+      </c>
+      <c r="K358" t="n">
+        <v>0</v>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Portland Timbers vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F359" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I359" t="n">
+        <v>0</v>
+      </c>
+      <c r="J359" t="n">
+        <v>0</v>
+      </c>
+      <c r="K359" t="n">
+        <v>0</v>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>South Cardiff vs Dudley Redhead United</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>South Cardiff</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F360" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I360" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" t="n">
+        <v>0</v>
+      </c>
+      <c r="K360" t="n">
+        <v>0</v>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Auckland vs Tottenham</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Tottenham</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F361" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I361" t="n">
+        <v>0</v>
+      </c>
+      <c r="J361" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" t="n">
+        <v>0</v>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Atletico San Luis</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Atletico San Luis</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F362" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I362" t="n">
+        <v>0</v>
+      </c>
+      <c r="J362" t="n">
+        <v>0</v>
+      </c>
+      <c r="K362" t="n">
+        <v>0</v>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Weston Bears vs Melbourne City</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Weston Bears</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F363" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J363" t="n">
+        <v>0</v>
+      </c>
+      <c r="K363" t="n">
+        <v>0</v>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Wollongong Wolves vs Blacktown City</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Blacktown City</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F364" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I364" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" t="n">
+        <v>0</v>
+      </c>
+      <c r="K364" t="n">
+        <v>0</v>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Kahibah vs Belmont Swansea</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Belmont Swansea</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F365" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" t="n">
+        <v>0</v>
+      </c>
+      <c r="K365" t="n">
+        <v>0</v>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Canberra Juventus vs Monaro Panthers</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Canberra Juventus</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E366" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F366" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J366" t="n">
+        <v>0</v>
+      </c>
+      <c r="K366" t="n">
+        <v>0</v>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Slavia Praha II vs Příbram</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Slavia Praha II</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E367" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F367" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J367" t="n">
+        <v>0</v>
+      </c>
+      <c r="K367" t="n">
+        <v>0</v>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Shanghai Port II vs Tai'an Tiankuang</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Shanghai Port II</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E368" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="F368" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I368" t="n">
+        <v>0</v>
+      </c>
+      <c r="J368" t="n">
+        <v>0</v>
+      </c>
+      <c r="K368" t="n">
+        <v>0</v>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>PSMS Medan vs Port FC</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Port FC</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E369" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F369" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I369" t="n">
+        <v>0</v>
+      </c>
+      <c r="J369" t="n">
+        <v>0</v>
+      </c>
+      <c r="K369" t="n">
+        <v>0</v>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Kolos Kovalivka II vs Prykarpattia</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Kolos Kovalivka II</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E370" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F370" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I370" t="n">
+        <v>0</v>
+      </c>
+      <c r="J370" t="n">
+        <v>0</v>
+      </c>
+      <c r="K370" t="n">
+        <v>0</v>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Gyori ETO II vs Tatabánya</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Gyori ETO II</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E371" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F371" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I371" t="n">
+        <v>0</v>
+      </c>
+      <c r="J371" t="n">
+        <v>0</v>
+      </c>
+      <c r="K371" t="n">
+        <v>0</v>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Peerless vs United</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F372" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I372" t="n">
+        <v>0</v>
+      </c>
+      <c r="J372" t="n">
+        <v>0</v>
+      </c>
+      <c r="K372" t="n">
+        <v>0</v>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Changwon City vs Jeonbuk Motors II</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Changwon City</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F373" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J373" t="n">
+        <v>0</v>
+      </c>
+      <c r="K373" t="n">
+        <v>0</v>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Dinamo Barnaul vs Khimik Dzerzhinsk</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Khimik Dzerzhinsk</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F374" t="n">
+        <v>66</v>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I374" t="n">
+        <v>0</v>
+      </c>
+      <c r="J374" t="n">
+        <v>0</v>
+      </c>
+      <c r="K374" t="n">
+        <v>0</v>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Haman vs Sejong SA</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Sejong SA</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F375" t="n">
+        <v>71</v>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" t="n">
+        <v>0</v>
+      </c>
+      <c r="K375" t="n">
+        <v>0</v>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Tsirang vs Transport United</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Transport United</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F376" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" t="n">
+        <v>0</v>
+      </c>
+      <c r="K376" t="n">
+        <v>0</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Incheon United vs Bucheon FC 1995</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Incheon United</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F377" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I377" t="n">
+        <v>0</v>
+      </c>
+      <c r="J377" t="n">
+        <v>0</v>
+      </c>
+      <c r="K377" t="n">
+        <v>0</v>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Gimpo Citizen vs Yongin City</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Yongin City</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F378" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I378" t="n">
+        <v>0</v>
+      </c>
+      <c r="J378" t="n">
+        <v>0</v>
+      </c>
+      <c r="K378" t="n">
+        <v>0</v>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Arsenal Tula II vs Ryazan</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Arsenal Tula II</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F379" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J379" t="n">
+        <v>0</v>
+      </c>
+      <c r="K379" t="n">
+        <v>0</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Kaluga vs Novosibirsk</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Kaluga</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F380" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I380" t="n">
+        <v>0</v>
+      </c>
+      <c r="J380" t="n">
+        <v>0</v>
+      </c>
+      <c r="K380" t="n">
+        <v>0</v>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Guimaraes vs Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F381" t="n">
+        <v>68.8</v>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I381" t="n">
+        <v>0</v>
+      </c>
+      <c r="J381" t="n">
+        <v>0</v>
+      </c>
+      <c r="K381" t="n">
+        <v>0</v>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Dinamo Minsk vs ML Vitebsk</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>ML Vitebsk</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F382" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I382" t="n">
+        <v>0</v>
+      </c>
+      <c r="J382" t="n">
+        <v>0</v>
+      </c>
+      <c r="K382" t="n">
+        <v>0</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Sirius vs IFK Goteborg</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Sirius</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F383" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" t="n">
+        <v>0</v>
+      </c>
+      <c r="K383" t="n">
+        <v>0</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Inter Turku vs Gnistan</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Inter Turku</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F384" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I384" t="n">
+        <v>0</v>
+      </c>
+      <c r="J384" t="n">
+        <v>0</v>
+      </c>
+      <c r="K384" t="n">
+        <v>0</v>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Super Nova vs Riga</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Super Nova</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F385" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I385" t="n">
+        <v>0</v>
+      </c>
+      <c r="J385" t="n">
+        <v>0</v>
+      </c>
+      <c r="K385" t="n">
+        <v>0</v>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Saku Sporting vs Legion</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Saku Sporting</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F386" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I386" t="n">
+        <v>0</v>
+      </c>
+      <c r="J386" t="n">
+        <v>0</v>
+      </c>
+      <c r="K386" t="n">
+        <v>0</v>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Ajax vs Burnley</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F387" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I387" t="n">
+        <v>0</v>
+      </c>
+      <c r="J387" t="n">
+        <v>0</v>
+      </c>
+      <c r="K387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Eintracht Norderstedt vs St. Pauli II</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Eintracht Norderstedt</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F388" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J388" t="n">
+        <v>0</v>
+      </c>
+      <c r="K388" t="n">
+        <v>0</v>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Ostia Mare vs Benevento</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Ostia Mare</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F389" t="n">
+        <v>63</v>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I389" t="n">
+        <v>0</v>
+      </c>
+      <c r="J389" t="n">
+        <v>0</v>
+      </c>
+      <c r="K389" t="n">
+        <v>0</v>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>FC Viktoria Köln vs SV Sandhausen</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>SV Sandhausen</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F390" t="n">
+        <v>82</v>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I390" t="n">
+        <v>0</v>
+      </c>
+      <c r="J390" t="n">
+        <v>0</v>
+      </c>
+      <c r="K390" t="n">
+        <v>0</v>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>BSG Chemie Leipzig vs SV Babelsberg 03</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>BSG Chemie Leipzig</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F391" t="n">
+        <v>78</v>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I391" t="n">
+        <v>0</v>
+      </c>
+      <c r="J391" t="n">
+        <v>0</v>
+      </c>
+      <c r="K391" t="n">
+        <v>0</v>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Karonga United vs Creck</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Karonga United</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F392" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I392" t="n">
+        <v>0</v>
+      </c>
+      <c r="J392" t="n">
+        <v>0</v>
+      </c>
+      <c r="K392" t="n">
+        <v>0</v>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>WIT Georgia vs Samgurali</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>WIT Georgia</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F393" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I393" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" t="n">
+        <v>0</v>
+      </c>
+      <c r="K393" t="n">
+        <v>0</v>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Raków Częstochowa vs Wisla Plock</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Raków Częstochowa</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F394" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" t="n">
+        <v>0</v>
+      </c>
+      <c r="K394" t="n">
+        <v>0</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>FK Tobol Kostanay vs Atyrau</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>FK Tobol Kostanay</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F395" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I395" t="n">
+        <v>0</v>
+      </c>
+      <c r="J395" t="n">
+        <v>0</v>
+      </c>
+      <c r="K395" t="n">
+        <v>0</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Juventus vs Paulista</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F396" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I396" t="n">
+        <v>0</v>
+      </c>
+      <c r="J396" t="n">
+        <v>0</v>
+      </c>
+      <c r="K396" t="n">
+        <v>0</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Linense vs Marília</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Linense</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F397" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I397" t="n">
+        <v>0</v>
+      </c>
+      <c r="J397" t="n">
+        <v>0</v>
+      </c>
+      <c r="K397" t="n">
+        <v>0</v>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Santo André vs São Caetano</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Santo André</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F398" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" t="n">
+        <v>0</v>
+      </c>
+      <c r="K398" t="n">
+        <v>0</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Slavia Praha vs Slovácko</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Slavia Praha</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F399" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I399" t="n">
+        <v>0</v>
+      </c>
+      <c r="J399" t="n">
+        <v>0</v>
+      </c>
+      <c r="K399" t="n">
+        <v>0</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Dinamo Bryansk vs Alaniya Vladikavkaz</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Alaniya Vladikavkaz</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F400" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I400" t="n">
+        <v>0</v>
+      </c>
+      <c r="J400" t="n">
+        <v>0</v>
+      </c>
+      <c r="K400" t="n">
+        <v>0</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>PEC Zwolle vs AEK Athens FC</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>AEK Athens FC</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F401" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I401" t="n">
+        <v>0</v>
+      </c>
+      <c r="J401" t="n">
+        <v>0</v>
+      </c>
+      <c r="K401" t="n">
+        <v>0</v>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Bulawayo Chiefs vs Kariba</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Bulawayo Chiefs</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F402" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I402" t="n">
+        <v>0</v>
+      </c>
+      <c r="J402" t="n">
+        <v>0</v>
+      </c>
+      <c r="K402" t="n">
+        <v>0</v>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Hunters vs Herentals</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Hunters</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F403" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I403" t="n">
+        <v>0</v>
+      </c>
+      <c r="J403" t="n">
+        <v>0</v>
+      </c>
+      <c r="K403" t="n">
+        <v>0</v>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Manica Diamonds vs Triangle United</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Triangle United</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F404" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I404" t="n">
+        <v>0</v>
+      </c>
+      <c r="J404" t="n">
+        <v>0</v>
+      </c>
+      <c r="K404" t="n">
+        <v>0</v>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Ngezi Platinum vs Hardrock</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Ngezi Platinum</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F405" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>0</v>
+      </c>
+      <c r="J405" t="n">
+        <v>0</v>
+      </c>
+      <c r="K405" t="n">
+        <v>0</v>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>TelOne vs CAPS United</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>CAPS United</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F406" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>0</v>
+      </c>
+      <c r="J406" t="n">
+        <v>0</v>
+      </c>
+      <c r="K406" t="n">
+        <v>0</v>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>America SP vs Itaquá Athletico Clube</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>America SP</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F407" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>0</v>
+      </c>
+      <c r="J407" t="n">
+        <v>0</v>
+      </c>
+      <c r="K407" t="n">
+        <v>0</v>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Yelimay Semey vs Kaisar</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Yelimay Semey</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F408" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>0</v>
+      </c>
+      <c r="J408" t="n">
+        <v>0</v>
+      </c>
+      <c r="K408" t="n">
+        <v>0</v>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>ST Mirren vs Dunfermline</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Dunfermline</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F409" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>0</v>
+      </c>
+      <c r="J409" t="n">
+        <v>0</v>
+      </c>
+      <c r="K409" t="n">
+        <v>0</v>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>FC Copenhagen vs Lyngby</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>FC Copenhagen</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F410" t="n">
+        <v>67.7</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>0</v>
+      </c>
+      <c r="J410" t="n">
+        <v>0</v>
+      </c>
+      <c r="K410" t="n">
+        <v>0</v>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Lokomotiv vs Akhmat</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Akhmat</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F411" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>0</v>
+      </c>
+      <c r="J411" t="n">
+        <v>0</v>
+      </c>
+      <c r="K411" t="n">
+        <v>0</v>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>UN Kaerjeng 97 vs F91 Dudelange</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>UN Kaerjeng 97</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F412" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>0</v>
+      </c>
+      <c r="J412" t="n">
+        <v>0</v>
+      </c>
+      <c r="K412" t="n">
+        <v>0</v>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Clydebank vs Partick</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Clydebank</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F413" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I413" t="n">
+        <v>0</v>
+      </c>
+      <c r="J413" t="n">
+        <v>0</v>
+      </c>
+      <c r="K413" t="n">
+        <v>0</v>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Gais vs Halmstad</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Gais</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F414" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>0</v>
+      </c>
+      <c r="J414" t="n">
+        <v>0</v>
+      </c>
+      <c r="K414" t="n">
+        <v>0</v>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Karlsruher SC vs Inter</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F415" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>0</v>
+      </c>
+      <c r="J415" t="n">
+        <v>0</v>
+      </c>
+      <c r="K415" t="n">
+        <v>0</v>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>FC Lugano vs FC Vaduz</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>FC Lugano</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F416" t="n">
+        <v>72</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I416" t="n">
+        <v>0</v>
+      </c>
+      <c r="J416" t="n">
+        <v>0</v>
+      </c>
+      <c r="K416" t="n">
+        <v>0</v>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>FC ST. Gallen vs FC Zurich</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>FC ST. Gallen</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F417" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I417" t="n">
+        <v>0</v>
+      </c>
+      <c r="J417" t="n">
+        <v>0</v>
+      </c>
+      <c r="K417" t="n">
+        <v>0</v>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Atlanta United II vs New York City II</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Atlanta United II</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F418" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I418" t="n">
+        <v>0</v>
+      </c>
+      <c r="J418" t="n">
+        <v>0</v>
+      </c>
+      <c r="K418" t="n">
+        <v>0</v>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Kaspiy vs Zhenys</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Zhenys</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F419" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>0</v>
+      </c>
+      <c r="J419" t="n">
+        <v>0</v>
+      </c>
+      <c r="K419" t="n">
+        <v>0</v>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Minsk II vs Uni Minsk</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Minsk II</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F420" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I420" t="n">
+        <v>0</v>
+      </c>
+      <c r="J420" t="n">
+        <v>0</v>
+      </c>
+      <c r="K420" t="n">
+        <v>0</v>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Cherepovets vs Iskra Smolensk</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Iskra Smolensk</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F421" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I421" t="n">
+        <v>0</v>
+      </c>
+      <c r="J421" t="n">
+        <v>0</v>
+      </c>
+      <c r="K421" t="n">
+        <v>0</v>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Sileks vs Bashkimi Kumanovo</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Bashkimi Kumanovo</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F422" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I422" t="n">
+        <v>0</v>
+      </c>
+      <c r="J422" t="n">
+        <v>0</v>
+      </c>
+      <c r="K422" t="n">
+        <v>0</v>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Ružomberok vs Dunajska Streda</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Ružomberok</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F423" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I423" t="n">
+        <v>0</v>
+      </c>
+      <c r="J423" t="n">
+        <v>0</v>
+      </c>
+      <c r="K423" t="n">
+        <v>0</v>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Žilina vs FK Košice</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>FK Košice</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F424" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I424" t="n">
+        <v>0</v>
+      </c>
+      <c r="J424" t="n">
+        <v>0</v>
+      </c>
+      <c r="K424" t="n">
+        <v>0</v>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Unia Skierniewice vs Stal Mielec</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Unia Skierniewice</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F425" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I425" t="n">
+        <v>0</v>
+      </c>
+      <c r="J425" t="n">
+        <v>0</v>
+      </c>
+      <c r="K425" t="n">
+        <v>0</v>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Imst vs TSV Hartberg</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Imst</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F426" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I426" t="n">
+        <v>0</v>
+      </c>
+      <c r="J426" t="n">
+        <v>0</v>
+      </c>
+      <c r="K426" t="n">
+        <v>0</v>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Iveria Khashuri vs Torpedo Kutaisi</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Iveria Khashuri</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F427" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I427" t="n">
+        <v>0</v>
+      </c>
+      <c r="J427" t="n">
+        <v>0</v>
+      </c>
+      <c r="K427" t="n">
+        <v>0</v>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>FC Sochi vs Arsenal Tula</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Arsenal Tula</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F428" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I428" t="n">
+        <v>0</v>
+      </c>
+      <c r="J428" t="n">
+        <v>0</v>
+      </c>
+      <c r="K428" t="n">
+        <v>0</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Belotin vs Nový Jičín</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Belotin</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F429" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I429" t="n">
+        <v>0</v>
+      </c>
+      <c r="J429" t="n">
+        <v>0</v>
+      </c>
+      <c r="K429" t="n">
+        <v>0</v>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>SK Krumvir vs Znojmo</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Znojmo</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F430" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I430" t="n">
+        <v>0</v>
+      </c>
+      <c r="J430" t="n">
+        <v>0</v>
+      </c>
+      <c r="K430" t="n">
+        <v>0</v>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Zabreh vs Hranice</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Zabreh</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F431" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I431" t="n">
+        <v>0</v>
+      </c>
+      <c r="J431" t="n">
+        <v>0</v>
+      </c>
+      <c r="K431" t="n">
+        <v>0</v>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Fenix vs Atenas</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Fenix</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F432" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I432" t="n">
+        <v>0</v>
+      </c>
+      <c r="J432" t="n">
+        <v>0</v>
+      </c>
+      <c r="K432" t="n">
+        <v>0</v>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Rodange 91 vs Mamer</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Rodange 91</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F433" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I433" t="n">
+        <v>0</v>
+      </c>
+      <c r="J433" t="n">
+        <v>0</v>
+      </c>
+      <c r="K433" t="n">
+        <v>0</v>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Politehnica UTM vs Zimbru</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Politehnica UTM</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F434" t="n">
+        <v>85.3</v>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I434" t="n">
+        <v>0</v>
+      </c>
+      <c r="J434" t="n">
+        <v>0</v>
+      </c>
+      <c r="K434" t="n">
+        <v>0</v>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Arsenal vs Neman</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F435" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I435" t="n">
+        <v>0</v>
+      </c>
+      <c r="J435" t="n">
+        <v>0</v>
+      </c>
+      <c r="K435" t="n">
+        <v>0</v>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>FS Jelgava vs FK Liepaja</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>FS Jelgava</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F436" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I436" t="n">
+        <v>0</v>
+      </c>
+      <c r="J436" t="n">
+        <v>0</v>
+      </c>
+      <c r="K436" t="n">
+        <v>0</v>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Majosi vs Paksi SE II</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Majosi</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F437" t="n">
+        <v>61</v>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I437" t="n">
+        <v>0</v>
+      </c>
+      <c r="J437" t="n">
+        <v>0</v>
+      </c>
+      <c r="K437" t="n">
+        <v>0</v>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Auda vs BFC Daugavpils</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>BFC Daugavpils</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F438" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I438" t="n">
+        <v>0</v>
+      </c>
+      <c r="J438" t="n">
+        <v>0</v>
+      </c>
+      <c r="K438" t="n">
+        <v>0</v>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Bravo vs Nafta</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Bravo</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F439" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I439" t="n">
+        <v>0</v>
+      </c>
+      <c r="J439" t="n">
+        <v>0</v>
+      </c>
+      <c r="K439" t="n">
+        <v>0</v>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Pisa vs PRO Vercelli</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>PRO Vercelli</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F440" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I440" t="n">
+        <v>0</v>
+      </c>
+      <c r="J440" t="n">
+        <v>0</v>
+      </c>
+      <c r="K440" t="n">
+        <v>0</v>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Lazio vs Flaminia</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F441" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I441" t="n">
+        <v>0</v>
+      </c>
+      <c r="J441" t="n">
+        <v>0</v>
+      </c>
+      <c r="K441" t="n">
+        <v>0</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Napoli vs Carrarese</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F442" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I442" t="n">
+        <v>0</v>
+      </c>
+      <c r="J442" t="n">
+        <v>0</v>
+      </c>
+      <c r="K442" t="n">
+        <v>0</v>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Frosinone vs Ascoli</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Frosinone</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F443" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I443" t="n">
+        <v>0</v>
+      </c>
+      <c r="J443" t="n">
+        <v>0</v>
+      </c>
+      <c r="K443" t="n">
+        <v>0</v>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Shkendija vs Skopje</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Skopje</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F444" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I444" t="n">
+        <v>0</v>
+      </c>
+      <c r="J444" t="n">
+        <v>0</v>
+      </c>
+      <c r="K444" t="n">
+        <v>0</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Dukla Banská Bystrica vs Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Dukla Banská Bystrica</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F445" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I445" t="n">
+        <v>0</v>
+      </c>
+      <c r="J445" t="n">
+        <v>0</v>
+      </c>
+      <c r="K445" t="n">
+        <v>0</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Varketili vs Rustavi</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Varketili</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F446" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I446" t="n">
+        <v>0</v>
+      </c>
+      <c r="J446" t="n">
+        <v>0</v>
+      </c>
+      <c r="K446" t="n">
+        <v>0</v>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Sireți vs Petrocub</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Sireți</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F447" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I447" t="n">
+        <v>0</v>
+      </c>
+      <c r="J447" t="n">
+        <v>0</v>
+      </c>
+      <c r="K447" t="n">
+        <v>0</v>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Sheriff Tiraspol vs Milsami Orhei</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Sheriff Tiraspol</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F448" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I448" t="n">
+        <v>0</v>
+      </c>
+      <c r="J448" t="n">
+        <v>0</v>
+      </c>
+      <c r="K448" t="n">
+        <v>0</v>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Aalesund vs Viking</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Viking</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F449" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I449" t="n">
+        <v>0</v>
+      </c>
+      <c r="J449" t="n">
+        <v>0</v>
+      </c>
+      <c r="K449" t="n">
+        <v>0</v>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Atletico Tucuman vs Independ. Rivadavia</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Atletico Tucuman</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F450" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I450" t="n">
+        <v>0</v>
+      </c>
+      <c r="J450" t="n">
+        <v>0</v>
+      </c>
+      <c r="K450" t="n">
+        <v>0</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>General Lamadrid vs Claypole</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>General Lamadrid</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F451" t="n">
+        <v>87.59999999999999</v>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I451" t="n">
+        <v>0</v>
+      </c>
+      <c r="J451" t="n">
+        <v>0</v>
+      </c>
+      <c r="K451" t="n">
+        <v>0</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Juventud Unida vs Defensores de Cambaceres</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Juventud Unida</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F452" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I452" t="n">
+        <v>0</v>
+      </c>
+      <c r="J452" t="n">
+        <v>0</v>
+      </c>
+      <c r="K452" t="n">
+        <v>0</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Juventude W vs Ferroviaria W</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Juventude W</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F453" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I453" t="n">
+        <v>0</v>
+      </c>
+      <c r="J453" t="n">
+        <v>0</v>
+      </c>
+      <c r="K453" t="n">
+        <v>0</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Atenas vs Juventud Unida Univ.</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Juventud Unida Univ.</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F454" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I454" t="n">
+        <v>0</v>
+      </c>
+      <c r="J454" t="n">
+        <v>0</v>
+      </c>
+      <c r="K454" t="n">
+        <v>0</v>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Sol de Mayo vs Villa Mitre</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Villa Mitre</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F455" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I455" t="n">
+        <v>0</v>
+      </c>
+      <c r="J455" t="n">
+        <v>0</v>
+      </c>
+      <c r="K455" t="n">
+        <v>0</v>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Sport Brasil ES vs Rive</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Sport Brasil ES</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F456" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>0</v>
+      </c>
+      <c r="J456" t="n">
+        <v>0</v>
+      </c>
+      <c r="K456" t="n">
+        <v>0</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Valeriodoce vs Villa Nova</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Villa Nova</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F457" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>0</v>
+      </c>
+      <c r="J457" t="n">
+        <v>0</v>
+      </c>
+      <c r="K457" t="n">
+        <v>0</v>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Aucas vs Macara</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Macara</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F458" t="n">
+        <v>83.2</v>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>0</v>
+      </c>
+      <c r="J458" t="n">
+        <v>0</v>
+      </c>
+      <c r="K458" t="n">
+        <v>0</v>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Koper vs Radomlje</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Koper</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F459" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>0</v>
+      </c>
+      <c r="J459" t="n">
+        <v>0</v>
+      </c>
+      <c r="K459" t="n">
+        <v>0</v>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Hope Internacional vs Iraty</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Hope Internacional</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F460" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I460" t="n">
+        <v>0</v>
+      </c>
+      <c r="J460" t="n">
+        <v>0</v>
+      </c>
+      <c r="K460" t="n">
+        <v>0</v>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Oeste Brasil vs Sport Club PR</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Sport Club PR</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="F461" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I461" t="n">
+        <v>0</v>
+      </c>
+      <c r="J461" t="n">
+        <v>0</v>
+      </c>
+      <c r="K461" t="n">
+        <v>0</v>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Wienerberg vs Rapid Vienna</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Wienerberg</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F462" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I462" t="n">
+        <v>0</v>
+      </c>
+      <c r="J462" t="n">
+        <v>0</v>
+      </c>
+      <c r="K462" t="n">
+        <v>0</v>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Atletico Mitre vs Almirante Brown</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Atletico Mitre</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F463" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I463" t="n">
+        <v>0</v>
+      </c>
+      <c r="J463" t="n">
+        <v>0</v>
+      </c>
+      <c r="K463" t="n">
+        <v>0</v>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Midland vs Patronato</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Midland</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F464" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I464" t="n">
+        <v>0</v>
+      </c>
+      <c r="J464" t="n">
+        <v>0</v>
+      </c>
+      <c r="K464" t="n">
+        <v>0</v>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Racing Cordoba vs San Telmo</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Racing Cordoba</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F465" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I465" t="n">
+        <v>0</v>
+      </c>
+      <c r="J465" t="n">
+        <v>0</v>
+      </c>
+      <c r="K465" t="n">
+        <v>0</v>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>São Bernardo vs Ceara</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F466" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I466" t="n">
+        <v>0</v>
+      </c>
+      <c r="J466" t="n">
+        <v>0</v>
+      </c>
+      <c r="K466" t="n">
+        <v>0</v>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Brusque vs Ituano</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F467" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I467" t="n">
+        <v>0</v>
+      </c>
+      <c r="J467" t="n">
+        <v>0</v>
+      </c>
+      <c r="K467" t="n">
+        <v>0</v>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Ypiranga-RS vs Barra</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Ypiranga-RS</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F468" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I468" t="n">
+        <v>0</v>
+      </c>
+      <c r="J468" t="n">
+        <v>0</v>
+      </c>
+      <c r="K468" t="n">
+        <v>0</v>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Macva vs FK Partizan</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>FK Partizan</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="F469" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I469" t="n">
+        <v>0</v>
+      </c>
+      <c r="J469" t="n">
+        <v>0</v>
+      </c>
+      <c r="K469" t="n">
+        <v>0</v>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Sevilla vs AD Ceuta FC</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F470" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I470" t="n">
+        <v>0</v>
+      </c>
+      <c r="J470" t="n">
+        <v>0</v>
+      </c>
+      <c r="K470" t="n">
+        <v>0</v>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>IA Akranes vs Stjarnan</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>IA Akranes</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F471" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+      <c r="J471" t="n">
+        <v>0</v>
+      </c>
+      <c r="K471" t="n">
+        <v>0</v>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Petare FC vs Aragua FC</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Petare FC</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F472" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I472" t="n">
+        <v>0</v>
+      </c>
+      <c r="J472" t="n">
+        <v>0</v>
+      </c>
+      <c r="K472" t="n">
+        <v>0</v>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Inter Willemstad vs St. John's</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Inter Willemstad</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F473" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I473" t="n">
+        <v>0</v>
+      </c>
+      <c r="J473" t="n">
+        <v>0</v>
+      </c>
+      <c r="K473" t="n">
+        <v>0</v>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Portland Timbers II vs Real Monarchs</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Real Monarchs</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F474" t="n">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I474" t="n">
+        <v>0</v>
+      </c>
+      <c r="J474" t="n">
+        <v>0</v>
+      </c>
+      <c r="K474" t="n">
+        <v>0</v>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Treze vs Sao Jose</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Treze</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F475" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I475" t="n">
+        <v>0</v>
+      </c>
+      <c r="J475" t="n">
+        <v>0</v>
+      </c>
+      <c r="K475" t="n">
+        <v>0</v>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Alianza Atletico vs UTC Cajamarca</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Alianza Atletico</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F476" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I476" t="n">
+        <v>0</v>
+      </c>
+      <c r="J476" t="n">
+        <v>0</v>
+      </c>
+      <c r="K476" t="n">
+        <v>0</v>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Atletico Grau vs Sport Boys</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Atletico Grau</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F477" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I477" t="n">
+        <v>0</v>
+      </c>
+      <c r="J477" t="n">
+        <v>0</v>
+      </c>
+      <c r="K477" t="n">
+        <v>0</v>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Estudiantes L.P. vs Independiente</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Estudiantes L.P.</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F478" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I478" t="n">
+        <v>0</v>
+      </c>
+      <c r="J478" t="n">
+        <v>0</v>
+      </c>
+      <c r="K478" t="n">
+        <v>0</v>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>York United vs Forge</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>York United</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F479" t="n">
+        <v>70.7</v>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I479" t="n">
+        <v>0</v>
+      </c>
+      <c r="J479" t="n">
+        <v>0</v>
+      </c>
+      <c r="K479" t="n">
+        <v>0</v>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Fuerte San Francisco vs Platense</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Fuerte San Francisco</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F480" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I480" t="n">
+        <v>0</v>
+      </c>
+      <c r="J480" t="n">
+        <v>0</v>
+      </c>
+      <c r="K480" t="n">
+        <v>0</v>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Flamengo vs Sao Paulo</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F481" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I481" t="n">
+        <v>0</v>
+      </c>
+      <c r="J481" t="n">
+        <v>0</v>
+      </c>
+      <c r="K481" t="n">
+        <v>0</v>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Gremio vs Fluminense</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Gremio</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F482" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I482" t="n">
+        <v>0</v>
+      </c>
+      <c r="J482" t="n">
+        <v>0</v>
+      </c>
+      <c r="K482" t="n">
+        <v>0</v>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>A. Italiano vs Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>A. Italiano</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F483" t="n">
+        <v>82</v>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I483" t="n">
+        <v>0</v>
+      </c>
+      <c r="J483" t="n">
+        <v>0</v>
+      </c>
+      <c r="K483" t="n">
+        <v>0</v>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>America Mineiro vs Goias</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>America Mineiro</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F484" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I484" t="n">
+        <v>0</v>
+      </c>
+      <c r="J484" t="n">
+        <v>0</v>
+      </c>
+      <c r="K484" t="n">
+        <v>0</v>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Londrina vs Novorizontino</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F485" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I485" t="n">
+        <v>0</v>
+      </c>
+      <c r="J485" t="n">
+        <v>0</v>
+      </c>
+      <c r="K485" t="n">
+        <v>0</v>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Minnesota United FC vs Liberia</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Minnesota United FC</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F486" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I486" t="n">
+        <v>0</v>
+      </c>
+      <c r="J486" t="n">
+        <v>0</v>
+      </c>
+      <c r="K486" t="n">
+        <v>0</v>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Miramar vs La Luz</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>La Luz</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F487" t="n">
+        <v>80</v>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I487" t="n">
+        <v>0</v>
+      </c>
+      <c r="J487" t="n">
+        <v>0</v>
+      </c>
+      <c r="K487" t="n">
+        <v>0</v>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Orlando City II vs Huntsville City</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Orlando City II</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F488" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I488" t="n">
+        <v>0</v>
+      </c>
+      <c r="J488" t="n">
+        <v>0</v>
+      </c>
+      <c r="K488" t="n">
+        <v>0</v>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>San Carlos vs Escorpiones Belén</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Escorpiones Belén</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F489" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I489" t="n">
+        <v>0</v>
+      </c>
+      <c r="J489" t="n">
+        <v>0</v>
+      </c>
+      <c r="K489" t="n">
+        <v>0</v>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Veraguas vs Independiente de La Chorrera</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Veraguas</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F490" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I490" t="n">
+        <v>0</v>
+      </c>
+      <c r="J490" t="n">
+        <v>0</v>
+      </c>
+      <c r="K490" t="n">
+        <v>0</v>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -18587,7 +25919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18663,6 +25995,28 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>141</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -25919,7 +25919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26018,6 +26018,25 @@
       </c>
       <c r="F4" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L490"/>
+  <dimension ref="A1:L547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25905,6 +25905,2970 @@
       <c r="L490" t="inlineStr">
         <is>
           <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Chelsea vs Western Sydney Wanderers</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F491" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>6-4</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I491" t="n">
+        <v>0</v>
+      </c>
+      <c r="J491" t="n">
+        <v>0</v>
+      </c>
+      <c r="K491" t="n">
+        <v>0</v>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Philippines vs Myanmar</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F492" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I492" t="n">
+        <v>0</v>
+      </c>
+      <c r="J492" t="n">
+        <v>0</v>
+      </c>
+      <c r="K492" t="n">
+        <v>0</v>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Nancy vs Annecy</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F493" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I493" t="n">
+        <v>0</v>
+      </c>
+      <c r="J493" t="n">
+        <v>0</v>
+      </c>
+      <c r="K493" t="n">
+        <v>0</v>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Mogadishu City vs Singida Black Stars</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Mogadishu City</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F494" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I494" t="n">
+        <v>0</v>
+      </c>
+      <c r="J494" t="n">
+        <v>0</v>
+      </c>
+      <c r="K494" t="n">
+        <v>0</v>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Nasaf vs Qizilqum</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Qizilqum</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F495" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I495" t="n">
+        <v>0</v>
+      </c>
+      <c r="J495" t="n">
+        <v>0</v>
+      </c>
+      <c r="K495" t="n">
+        <v>0</v>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Xorazm vs Surkhon</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Xorazm</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F496" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I496" t="n">
+        <v>0</v>
+      </c>
+      <c r="J496" t="n">
+        <v>0</v>
+      </c>
+      <c r="K496" t="n">
+        <v>0</v>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Cagliari vs Modena</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F497" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I497" t="n">
+        <v>0</v>
+      </c>
+      <c r="J497" t="n">
+        <v>0</v>
+      </c>
+      <c r="K497" t="n">
+        <v>0</v>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>KuPS vs Sabah FA</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F498" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I498" t="n">
+        <v>0</v>
+      </c>
+      <c r="J498" t="n">
+        <v>0</v>
+      </c>
+      <c r="K498" t="n">
+        <v>0</v>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Vihren vs CSKA Sofia II</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Vihren</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F499" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I499" t="n">
+        <v>0</v>
+      </c>
+      <c r="J499" t="n">
+        <v>0</v>
+      </c>
+      <c r="K499" t="n">
+        <v>0</v>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>Kozuv Gevgelija vs Belasica</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Kozuv Gevgelija</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F500" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I500" t="n">
+        <v>0</v>
+      </c>
+      <c r="J500" t="n">
+        <v>0</v>
+      </c>
+      <c r="K500" t="n">
+        <v>0</v>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Udinese vs Shabab Al Ahli Dubai</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F501" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I501" t="n">
+        <v>0</v>
+      </c>
+      <c r="J501" t="n">
+        <v>0</v>
+      </c>
+      <c r="K501" t="n">
+        <v>0</v>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Rouen vs Al Wakrah</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Rouen</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F502" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I502" t="n">
+        <v>0</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0</v>
+      </c>
+      <c r="K502" t="n">
+        <v>0</v>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Jamus vs Simba</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Jamus</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F503" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I503" t="n">
+        <v>0</v>
+      </c>
+      <c r="J503" t="n">
+        <v>0</v>
+      </c>
+      <c r="K503" t="n">
+        <v>0</v>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Mladost Ždralovi vs Inter Zapresic</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Inter Zapresic</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F504" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I504" t="n">
+        <v>0</v>
+      </c>
+      <c r="J504" t="n">
+        <v>0</v>
+      </c>
+      <c r="K504" t="n">
+        <v>0</v>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>OFK Beograd vs Gaziantep FK</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>OFK Beograd</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F505" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I505" t="n">
+        <v>0</v>
+      </c>
+      <c r="J505" t="n">
+        <v>0</v>
+      </c>
+      <c r="K505" t="n">
+        <v>0</v>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Real Madrid vs Leganes</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F506" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I506" t="n">
+        <v>0</v>
+      </c>
+      <c r="J506" t="n">
+        <v>0</v>
+      </c>
+      <c r="K506" t="n">
+        <v>0</v>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>FC Tallinn vs Tallinna FC Zapoos</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Tallinna FC Zapoos</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F507" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I507" t="n">
+        <v>0</v>
+      </c>
+      <c r="J507" t="n">
+        <v>0</v>
+      </c>
+      <c r="K507" t="n">
+        <v>0</v>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Riga vs Vardar Skopje</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Riga</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F508" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I508" t="n">
+        <v>0</v>
+      </c>
+      <c r="J508" t="n">
+        <v>0</v>
+      </c>
+      <c r="K508" t="n">
+        <v>0</v>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Apollon Limassol vs Dila</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Apollon Limassol</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F509" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I509" t="n">
+        <v>0</v>
+      </c>
+      <c r="J509" t="n">
+        <v>0</v>
+      </c>
+      <c r="K509" t="n">
+        <v>0</v>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Al-Ahli Jeddah vs Fulham</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F510" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I510" t="n">
+        <v>0</v>
+      </c>
+      <c r="J510" t="n">
+        <v>0</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0</v>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>B36 Torshavn vs AB</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="F511" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I511" t="n">
+        <v>0</v>
+      </c>
+      <c r="J511" t="n">
+        <v>0</v>
+      </c>
+      <c r="K511" t="n">
+        <v>0</v>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Morecambe vs AFC Fylde</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>AFC Fylde</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F512" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I512" t="n">
+        <v>0</v>
+      </c>
+      <c r="J512" t="n">
+        <v>0</v>
+      </c>
+      <c r="K512" t="n">
+        <v>0</v>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>GEL vs Linhares</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>GEL</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F513" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I513" t="n">
+        <v>0</v>
+      </c>
+      <c r="J513" t="n">
+        <v>0</v>
+      </c>
+      <c r="K513" t="n">
+        <v>0</v>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Grimsby vs Lincoln</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Grimsby</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F514" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I514" t="n">
+        <v>0</v>
+      </c>
+      <c r="J514" t="n">
+        <v>0</v>
+      </c>
+      <c r="K514" t="n">
+        <v>0</v>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Wealdstone vs AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Wealdstone</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F515" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I515" t="n">
+        <v>0</v>
+      </c>
+      <c r="J515" t="n">
+        <v>0</v>
+      </c>
+      <c r="K515" t="n">
+        <v>0</v>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Oldham vs Stockport County</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Oldham</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F516" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I516" t="n">
+        <v>0</v>
+      </c>
+      <c r="J516" t="n">
+        <v>0</v>
+      </c>
+      <c r="K516" t="n">
+        <v>0</v>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Drita vs Floriana</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Drita</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F517" t="n">
+        <v>71.3</v>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I517" t="n">
+        <v>0</v>
+      </c>
+      <c r="J517" t="n">
+        <v>0</v>
+      </c>
+      <c r="K517" t="n">
+        <v>0</v>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Cambridge United vs Northampton</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Cambridge United</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F518" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I518" t="n">
+        <v>0</v>
+      </c>
+      <c r="J518" t="n">
+        <v>1</v>
+      </c>
+      <c r="K518" t="n">
+        <v>0</v>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Gateshead vs South Shields</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>South Shields</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F519" t="n">
+        <v>71.90000000000001</v>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I519" t="n">
+        <v>0</v>
+      </c>
+      <c r="J519" t="n">
+        <v>0</v>
+      </c>
+      <c r="K519" t="n">
+        <v>0</v>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Aston Villa vs Real Sociedad</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F520" t="n">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I520" t="n">
+        <v>0</v>
+      </c>
+      <c r="J520" t="n">
+        <v>0</v>
+      </c>
+      <c r="K520" t="n">
+        <v>0</v>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Carrick Rangers vs Ards</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Carrick Rangers</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F521" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I521" t="n">
+        <v>0</v>
+      </c>
+      <c r="J521" t="n">
+        <v>0</v>
+      </c>
+      <c r="K521" t="n">
+        <v>0</v>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Dagenham &amp; Redbridge vs Boreham Wood</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F522" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I522" t="n">
+        <v>0</v>
+      </c>
+      <c r="J522" t="n">
+        <v>0</v>
+      </c>
+      <c r="K522" t="n">
+        <v>0</v>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Dollingstown vs Linfield</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Dollingstown</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="F523" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I523" t="n">
+        <v>0</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0</v>
+      </c>
+      <c r="L523" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Moyola Park vs Limavady United</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Limavady United</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F524" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I524" t="n">
+        <v>0</v>
+      </c>
+      <c r="J524" t="n">
+        <v>0</v>
+      </c>
+      <c r="K524" t="n">
+        <v>0</v>
+      </c>
+      <c r="L524" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Newry City AFC vs Bangor</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Bangor</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F525" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I525" t="n">
+        <v>0</v>
+      </c>
+      <c r="J525" t="n">
+        <v>0</v>
+      </c>
+      <c r="K525" t="n">
+        <v>0</v>
+      </c>
+      <c r="L525" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>York vs Peterborough</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>York</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F526" t="n">
+        <v>86.59999999999999</v>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I526" t="n">
+        <v>0</v>
+      </c>
+      <c r="J526" t="n">
+        <v>0</v>
+      </c>
+      <c r="K526" t="n">
+        <v>0</v>
+      </c>
+      <c r="L526" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Felixstowe &amp; Walton Utd vs Braintree</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Felixstowe &amp; Walton Utd</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F527" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I527" t="n">
+        <v>0</v>
+      </c>
+      <c r="J527" t="n">
+        <v>0</v>
+      </c>
+      <c r="K527" t="n">
+        <v>0</v>
+      </c>
+      <c r="L527" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Merthyr Town vs Swansea</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Swansea</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F528" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I528" t="n">
+        <v>0</v>
+      </c>
+      <c r="J528" t="n">
+        <v>0</v>
+      </c>
+      <c r="K528" t="n">
+        <v>0</v>
+      </c>
+      <c r="L528" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Marine vs Warrington Town</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Marine</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F529" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I529" t="n">
+        <v>0</v>
+      </c>
+      <c r="J529" t="n">
+        <v>0</v>
+      </c>
+      <c r="K529" t="n">
+        <v>0</v>
+      </c>
+      <c r="L529" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Dartford vs Chelmsford City</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Chelmsford City</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="F530" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I530" t="n">
+        <v>0</v>
+      </c>
+      <c r="J530" t="n">
+        <v>0</v>
+      </c>
+      <c r="K530" t="n">
+        <v>0</v>
+      </c>
+      <c r="L530" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Farnham Town vs Yeovil Town</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Yeovil Town</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F531" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I531" t="n">
+        <v>0</v>
+      </c>
+      <c r="J531" t="n">
+        <v>0</v>
+      </c>
+      <c r="K531" t="n">
+        <v>0</v>
+      </c>
+      <c r="L531" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Crusaders FC vs Newington Youth</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Crusaders FC</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F532" t="n">
+        <v>72.40000000000001</v>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I532" t="n">
+        <v>0</v>
+      </c>
+      <c r="J532" t="n">
+        <v>0</v>
+      </c>
+      <c r="K532" t="n">
+        <v>0</v>
+      </c>
+      <c r="L532" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Hereford vs Shrewsbury</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Hereford</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F533" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I533" t="n">
+        <v>0</v>
+      </c>
+      <c r="J533" t="n">
+        <v>0</v>
+      </c>
+      <c r="K533" t="n">
+        <v>0</v>
+      </c>
+      <c r="L533" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Colchester vs Charlton</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Colchester</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F534" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I534" t="n">
+        <v>0</v>
+      </c>
+      <c r="J534" t="n">
+        <v>0</v>
+      </c>
+      <c r="K534" t="n">
+        <v>0</v>
+      </c>
+      <c r="L534" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Enfield Town vs AFC Hornchurch</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>AFC Hornchurch</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F535" t="n">
+        <v>73.59999999999999</v>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I535" t="n">
+        <v>0</v>
+      </c>
+      <c r="J535" t="n">
+        <v>0</v>
+      </c>
+      <c r="K535" t="n">
+        <v>0</v>
+      </c>
+      <c r="L535" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Nantwich Town vs Chester</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Chester</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F536" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I536" t="n">
+        <v>0</v>
+      </c>
+      <c r="J536" t="n">
+        <v>0</v>
+      </c>
+      <c r="K536" t="n">
+        <v>0</v>
+      </c>
+      <c r="L536" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Stoke City vs Everton</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F537" t="n">
+        <v>79.90000000000001</v>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I537" t="n">
+        <v>0</v>
+      </c>
+      <c r="J537" t="n">
+        <v>0</v>
+      </c>
+      <c r="K537" t="n">
+        <v>0</v>
+      </c>
+      <c r="L537" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Celtic II vs Clydebank</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Celtic II</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F538" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I538" t="n">
+        <v>0</v>
+      </c>
+      <c r="J538" t="n">
+        <v>0</v>
+      </c>
+      <c r="K538" t="n">
+        <v>0</v>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Bromsgrove Sporting vs Malvern Town</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Bromsgrove Sporting</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F539" t="n">
+        <v>89</v>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I539" t="n">
+        <v>0</v>
+      </c>
+      <c r="J539" t="n">
+        <v>0</v>
+      </c>
+      <c r="K539" t="n">
+        <v>0</v>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Chertsey Town vs Chesham United</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Chesham United</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F540" t="n">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I540" t="n">
+        <v>0</v>
+      </c>
+      <c r="J540" t="n">
+        <v>0</v>
+      </c>
+      <c r="K540" t="n">
+        <v>0</v>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Cray Valley PM vs Ebbsfleet United</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Cray Valley PM</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="F541" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I541" t="n">
+        <v>0</v>
+      </c>
+      <c r="J541" t="n">
+        <v>0</v>
+      </c>
+      <c r="K541" t="n">
+        <v>0</v>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Halesowen Town vs Stourbridge</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Stourbridge</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F542" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I542" t="n">
+        <v>0</v>
+      </c>
+      <c r="J542" t="n">
+        <v>0</v>
+      </c>
+      <c r="K542" t="n">
+        <v>0</v>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Ilkeston Town vs Basford United</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Basford United</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F543" t="n">
+        <v>88.2</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I543" t="n">
+        <v>0</v>
+      </c>
+      <c r="J543" t="n">
+        <v>0</v>
+      </c>
+      <c r="K543" t="n">
+        <v>0</v>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Maidstone Utd vs Brentwood Town</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Maidstone Utd</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F544" t="n">
+        <v>67.8</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I544" t="n">
+        <v>0</v>
+      </c>
+      <c r="J544" t="n">
+        <v>0</v>
+      </c>
+      <c r="K544" t="n">
+        <v>0</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Cacahuatique vs Atletico Balboa</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Atletico Balboa</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F545" t="n">
+        <v>67.2</v>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I545" t="n">
+        <v>0</v>
+      </c>
+      <c r="J545" t="n">
+        <v>0</v>
+      </c>
+      <c r="K545" t="n">
+        <v>0</v>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Juventude vs Avai</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F546" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I546" t="n">
+        <v>0</v>
+      </c>
+      <c r="J546" t="n">
+        <v>1</v>
+      </c>
+      <c r="K546" t="n">
+        <v>0</v>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Ponte Preta vs Athletic Club</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F547" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I547" t="n">
+        <v>0</v>
+      </c>
+      <c r="J547" t="n">
+        <v>0</v>
+      </c>
+      <c r="K547" t="n">
+        <v>0</v>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>sí</t>
         </is>
       </c>
     </row>
@@ -25919,7 +28883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26037,6 +29001,28 @@
       </c>
       <c r="F5" t="n">
         <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>57</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L547"/>
+  <dimension ref="A1:L588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28869,6 +28869,2138 @@
       <c r="L547" t="inlineStr">
         <is>
           <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Kansas City W vs Racing Louisville W</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Kansas City W</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F548" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I548" t="n">
+        <v>0</v>
+      </c>
+      <c r="J548" t="n">
+        <v>0</v>
+      </c>
+      <c r="K548" t="n">
+        <v>0</v>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Fluminense vs Bahia</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F549" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I549" t="n">
+        <v>0</v>
+      </c>
+      <c r="J549" t="n">
+        <v>0</v>
+      </c>
+      <c r="K549" t="n">
+        <v>0</v>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Instituto Cordoba vs Platense</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Instituto Cordoba</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F550" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>✅</t>
+        </is>
+      </c>
+      <c r="I550" t="n">
+        <v>0</v>
+      </c>
+      <c r="J550" t="n">
+        <v>0</v>
+      </c>
+      <c r="K550" t="n">
+        <v>0</v>
+      </c>
+      <c r="L550" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Cienciano vs Lanus</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F551" t="n">
+        <v>80.40000000000001</v>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I551" t="n">
+        <v>0</v>
+      </c>
+      <c r="J551" t="n">
+        <v>0</v>
+      </c>
+      <c r="K551" t="n">
+        <v>1</v>
+      </c>
+      <c r="L551" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Vancouver Rise W vs Montreal Roses W</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Vancouver Rise W</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F552" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I552" t="n">
+        <v>0</v>
+      </c>
+      <c r="J552" t="n">
+        <v>0</v>
+      </c>
+      <c r="K552" t="n">
+        <v>0</v>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Alianza vs Antigua GFC</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Antigua GFC</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F553" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>❌</t>
+        </is>
+      </c>
+      <c r="I553" t="n">
+        <v>0</v>
+      </c>
+      <c r="J553" t="n">
+        <v>1</v>
+      </c>
+      <c r="K553" t="n">
+        <v>0</v>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Anri Vladivostok vs Dinamo Barnaul</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Anri Vladivostok</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F554" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I554" t="n">
+        <v>0</v>
+      </c>
+      <c r="J554" t="n">
+        <v>0</v>
+      </c>
+      <c r="K554" t="n">
+        <v>0</v>
+      </c>
+      <c r="L554" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>South Melbourne vs Adelaide United</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>South Melbourne</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F555" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I555" t="n">
+        <v>0</v>
+      </c>
+      <c r="J555" t="n">
+        <v>0</v>
+      </c>
+      <c r="K555" t="n">
+        <v>0</v>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Ekibastuz vs Yelimay Semey 2</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Ekibastuz</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F556" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I556" t="n">
+        <v>0</v>
+      </c>
+      <c r="J556" t="n">
+        <v>0</v>
+      </c>
+      <c r="K556" t="n">
+        <v>1</v>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Viking U19 vs Lyn U19</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Viking U19</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F557" t="n">
+        <v>60.9</v>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I557" t="n">
+        <v>0</v>
+      </c>
+      <c r="J557" t="n">
+        <v>0</v>
+      </c>
+      <c r="K557" t="n">
+        <v>0</v>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Shortan vs Respublika FA</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Shortan</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F558" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I558" t="n">
+        <v>0</v>
+      </c>
+      <c r="J558" t="n">
+        <v>0</v>
+      </c>
+      <c r="K558" t="n">
+        <v>0</v>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>FK Tobol Kostanay vs Panevėžys</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>FK Tobol Kostanay</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F559" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I559" t="n">
+        <v>0</v>
+      </c>
+      <c r="J559" t="n">
+        <v>0</v>
+      </c>
+      <c r="K559" t="n">
+        <v>0</v>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>FC Augsburg vs Bournemouth</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Bournemouth</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F560" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I560" t="n">
+        <v>0</v>
+      </c>
+      <c r="J560" t="n">
+        <v>0</v>
+      </c>
+      <c r="K560" t="n">
+        <v>0</v>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Atlètic Club d'Escaldes vs FC Vaduz</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>FC Vaduz</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F561" t="n">
+        <v>61.8</v>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I561" t="n">
+        <v>0</v>
+      </c>
+      <c r="J561" t="n">
+        <v>0</v>
+      </c>
+      <c r="K561" t="n">
+        <v>0</v>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Cavese vs Sarnese</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Sarnese</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F562" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I562" t="n">
+        <v>0</v>
+      </c>
+      <c r="J562" t="n">
+        <v>0</v>
+      </c>
+      <c r="K562" t="n">
+        <v>0</v>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>FC jazz vs KuPS Akatemia</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>FC jazz</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="F563" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I563" t="n">
+        <v>0</v>
+      </c>
+      <c r="J563" t="n">
+        <v>0</v>
+      </c>
+      <c r="K563" t="n">
+        <v>0</v>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Auda vs FCSB</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>FCSB</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F564" t="n">
+        <v>64.7</v>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I564" t="n">
+        <v>0</v>
+      </c>
+      <c r="J564" t="n">
+        <v>0</v>
+      </c>
+      <c r="K564" t="n">
+        <v>0</v>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>FC Noah vs Zimbru</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>FC Noah</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F565" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I565" t="n">
+        <v>0</v>
+      </c>
+      <c r="J565" t="n">
+        <v>0</v>
+      </c>
+      <c r="K565" t="n">
+        <v>0</v>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Monza vs Aris Thessalonikis</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="F566" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I566" t="n">
+        <v>0</v>
+      </c>
+      <c r="J566" t="n">
+        <v>0</v>
+      </c>
+      <c r="K566" t="n">
+        <v>0</v>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Ilves vs Stjarnan</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Ilves</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="F567" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I567" t="n">
+        <v>0</v>
+      </c>
+      <c r="J567" t="n">
+        <v>0</v>
+      </c>
+      <c r="K567" t="n">
+        <v>0</v>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Kalju Nomme vs Shelbourne</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Kalju Nomme</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F568" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I568" t="n">
+        <v>0</v>
+      </c>
+      <c r="J568" t="n">
+        <v>0</v>
+      </c>
+      <c r="K568" t="n">
+        <v>0</v>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Marseille vs Nimes</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Marseille</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F569" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I569" t="n">
+        <v>0</v>
+      </c>
+      <c r="J569" t="n">
+        <v>0</v>
+      </c>
+      <c r="K569" t="n">
+        <v>0</v>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>HB Torshavn vs Motherwell</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="F570" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I570" t="n">
+        <v>0</v>
+      </c>
+      <c r="J570" t="n">
+        <v>0</v>
+      </c>
+      <c r="K570" t="n">
+        <v>0</v>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Malaga vs Al-Ittihad FC</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F571" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I571" t="n">
+        <v>0</v>
+      </c>
+      <c r="J571" t="n">
+        <v>0</v>
+      </c>
+      <c r="K571" t="n">
+        <v>0</v>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Valletta FC vs Raków Częstochowa</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Raków Częstochowa</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F572" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I572" t="n">
+        <v>0</v>
+      </c>
+      <c r="J572" t="n">
+        <v>0</v>
+      </c>
+      <c r="K572" t="n">
+        <v>0</v>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>PAOK vs Dynamo Kyiv</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F573" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I573" t="n">
+        <v>0</v>
+      </c>
+      <c r="J573" t="n">
+        <v>0</v>
+      </c>
+      <c r="K573" t="n">
+        <v>0</v>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Ludogorets vs Hapoel Tel Aviv</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Ludogorets</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F574" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I574" t="n">
+        <v>0</v>
+      </c>
+      <c r="J574" t="n">
+        <v>0</v>
+      </c>
+      <c r="K574" t="n">
+        <v>0</v>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Ajax vs Vojvodina</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F575" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I575" t="n">
+        <v>0</v>
+      </c>
+      <c r="J575" t="n">
+        <v>0</v>
+      </c>
+      <c r="K575" t="n">
+        <v>0</v>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>UNA Strassen vs FK Partizan</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>FK Partizan</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F576" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I576" t="n">
+        <v>0</v>
+      </c>
+      <c r="J576" t="n">
+        <v>0</v>
+      </c>
+      <c r="K576" t="n">
+        <v>0</v>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Panathinaikos vs Paks</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F577" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I577" t="n">
+        <v>0</v>
+      </c>
+      <c r="J577" t="n">
+        <v>0</v>
+      </c>
+      <c r="K577" t="n">
+        <v>0</v>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Austria Vienna vs FK Liepaja</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Austria Vienna</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F578" t="n">
+        <v>69.8</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I578" t="n">
+        <v>0</v>
+      </c>
+      <c r="J578" t="n">
+        <v>0</v>
+      </c>
+      <c r="K578" t="n">
+        <v>0</v>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>CFR 1907 Cluj vs Alashkert</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>CFR 1907 Cluj</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F579" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I579" t="n">
+        <v>0</v>
+      </c>
+      <c r="J579" t="n">
+        <v>0</v>
+      </c>
+      <c r="K579" t="n">
+        <v>0</v>
+      </c>
+      <c r="L579" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>GKS Katowice vs Žilina</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>GKS Katowice</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F580" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I580" t="n">
+        <v>0</v>
+      </c>
+      <c r="J580" t="n">
+        <v>0</v>
+      </c>
+      <c r="K580" t="n">
+        <v>0</v>
+      </c>
+      <c r="L580" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Koper vs NSI Runavik</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Koper</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F581" t="n">
+        <v>81</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I581" t="n">
+        <v>0</v>
+      </c>
+      <c r="J581" t="n">
+        <v>0</v>
+      </c>
+      <c r="K581" t="n">
+        <v>0</v>
+      </c>
+      <c r="L581" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>SC Braga vs Železničar Pančevo</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>SC Braga</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F582" t="n">
+        <v>89</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I582" t="n">
+        <v>0</v>
+      </c>
+      <c r="J582" t="n">
+        <v>0</v>
+      </c>
+      <c r="K582" t="n">
+        <v>0</v>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Benfica vs FC ST. Gallen</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F583" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I583" t="n">
+        <v>0</v>
+      </c>
+      <c r="J583" t="n">
+        <v>0</v>
+      </c>
+      <c r="K583" t="n">
+        <v>0</v>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Hibernian vs Malisheva</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F584" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I584" t="n">
+        <v>0</v>
+      </c>
+      <c r="J584" t="n">
+        <v>0</v>
+      </c>
+      <c r="K584" t="n">
+        <v>0</v>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Sutjeska vs ML Vitebsk</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>ML Vitebsk</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="F585" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I585" t="n">
+        <v>0</v>
+      </c>
+      <c r="J585" t="n">
+        <v>0</v>
+      </c>
+      <c r="K585" t="n">
+        <v>0</v>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Mexico U23 vs Venezuela U23</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Venezuela U23</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F586" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I586" t="n">
+        <v>0</v>
+      </c>
+      <c r="J586" t="n">
+        <v>0</v>
+      </c>
+      <c r="K586" t="n">
+        <v>0</v>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Atletico FC vs LDU Portoviejo</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Atletico FC</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F587" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I587" t="n">
+        <v>0</v>
+      </c>
+      <c r="J587" t="n">
+        <v>0</v>
+      </c>
+      <c r="K587" t="n">
+        <v>0</v>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Jalapa vs Real Estelí</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Jalapa</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="F588" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>sin resolver</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="I588" t="n">
+        <v>0</v>
+      </c>
+      <c r="J588" t="n">
+        <v>0</v>
+      </c>
+      <c r="K588" t="n">
+        <v>0</v>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -28883,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29022,6 +31154,28 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>41</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>40</v>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31177,6 +31177,25 @@
       </c>
       <c r="F7" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31195,6 +31195,25 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31214,6 +31214,25 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31233,6 +31233,25 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31252,6 +31252,25 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31271,6 +31271,25 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31290,6 +31290,25 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31309,6 +31309,25 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31328,6 +31328,25 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31347,6 +31347,25 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31366,6 +31366,25 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31385,6 +31385,25 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31404,6 +31404,25 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31423,6 +31423,25 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31442,6 +31442,25 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31461,6 +31461,25 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31480,6 +31480,25 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31499,6 +31499,25 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31518,6 +31518,25 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31537,6 +31537,25 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31556,6 +31556,25 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31575,6 +31575,25 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31594,6 +31594,25 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31613,6 +31613,25 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31632,6 +31632,25 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31651,6 +31651,25 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31670,6 +31670,25 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31689,6 +31689,25 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31708,6 +31708,25 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31727,6 +31727,25 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
         <v>100</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -31015,7 +31015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31746,6 +31746,25 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
         <v>100</v>
       </c>
     </row>
